--- a/Team-Data/2008-09/11-23-2008-09.xlsx
+++ b/Team-Data/2008-09/11-23-2008-09.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -742,10 +809,10 @@
         <v>9</v>
       </c>
       <c r="AE2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AF2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG2" t="n">
         <v>9</v>
@@ -754,10 +821,10 @@
         <v>20</v>
       </c>
       <c r="AI2" t="n">
+        <v>18</v>
+      </c>
+      <c r="AJ2" t="n">
         <v>17</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>16</v>
       </c>
       <c r="AK2" t="n">
         <v>15</v>
@@ -772,7 +839,7 @@
         <v>1</v>
       </c>
       <c r="AO2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AP2" t="n">
         <v>16</v>
@@ -787,19 +854,19 @@
         <v>20</v>
       </c>
       <c r="AT2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AU2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AV2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AW2" t="n">
         <v>19</v>
       </c>
       <c r="AX2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AY2" t="n">
         <v>19</v>
@@ -811,10 +878,10 @@
         <v>22</v>
       </c>
       <c r="BB2" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="BC2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BD2" t="n">
         <v>10</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>11-23-2008-09</t>
+          <t>2008-11-23</t>
         </is>
       </c>
     </row>
@@ -858,52 +925,52 @@
         <v>48.4</v>
       </c>
       <c r="I3" t="n">
-        <v>35</v>
+        <v>34.1</v>
       </c>
       <c r="J3" t="n">
-        <v>75.2</v>
+        <v>75.3</v>
       </c>
       <c r="K3" t="n">
-        <v>0.465</v>
+        <v>0.454</v>
       </c>
       <c r="L3" t="n">
-        <v>5.6</v>
+        <v>5.1</v>
       </c>
       <c r="M3" t="n">
-        <v>16.1</v>
+        <v>15.9</v>
       </c>
       <c r="N3" t="n">
-        <v>0.35</v>
+        <v>0.323</v>
       </c>
       <c r="O3" t="n">
-        <v>22.1</v>
+        <v>22.3</v>
       </c>
       <c r="P3" t="n">
-        <v>29.4</v>
+        <v>29.7</v>
       </c>
       <c r="Q3" t="n">
         <v>0.75</v>
       </c>
       <c r="R3" t="n">
-        <v>10.4</v>
+        <v>10.5</v>
       </c>
       <c r="S3" t="n">
-        <v>33.1</v>
+        <v>32.9</v>
       </c>
       <c r="T3" t="n">
-        <v>43.6</v>
+        <v>43.4</v>
       </c>
       <c r="U3" t="n">
-        <v>20.7</v>
+        <v>20.4</v>
       </c>
       <c r="V3" t="n">
         <v>16.9</v>
       </c>
       <c r="W3" t="n">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="X3" t="n">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="Y3" t="n">
         <v>3.9</v>
@@ -912,13 +979,13 @@
         <v>23.6</v>
       </c>
       <c r="AA3" t="n">
-        <v>24.7</v>
+        <v>24.8</v>
       </c>
       <c r="AB3" t="n">
-        <v>97.7</v>
+        <v>95.7</v>
       </c>
       <c r="AC3" t="n">
-        <v>7.4</v>
+        <v>6.7</v>
       </c>
       <c r="AD3" t="n">
         <v>2</v>
@@ -936,25 +1003,25 @@
         <v>15</v>
       </c>
       <c r="AI3" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="AJ3" t="n">
         <v>28</v>
       </c>
       <c r="AK3" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AL3" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AM3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AN3" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AO3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AP3" t="n">
         <v>3</v>
@@ -966,13 +1033,13 @@
         <v>23</v>
       </c>
       <c r="AS3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AT3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AU3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AV3" t="n">
         <v>30</v>
@@ -981,19 +1048,19 @@
         <v>7</v>
       </c>
       <c r="AX3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AY3" t="n">
         <v>5</v>
       </c>
       <c r="AZ3" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BA3" t="n">
         <v>3</v>
       </c>
       <c r="BB3" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="BC3" t="n">
         <v>3</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>11-23-2008-09</t>
+          <t>2008-11-23</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1170,7 @@
         <v>-5.3</v>
       </c>
       <c r="AD4" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AE4" t="n">
         <v>26</v>
@@ -1124,13 +1191,13 @@
         <v>29</v>
       </c>
       <c r="AK4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AL4" t="n">
         <v>26</v>
       </c>
       <c r="AM4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AN4" t="n">
         <v>25</v>
@@ -1142,7 +1209,7 @@
         <v>14</v>
       </c>
       <c r="AQ4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AR4" t="n">
         <v>15</v>
@@ -1151,16 +1218,16 @@
         <v>30</v>
       </c>
       <c r="AT4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AU4" t="n">
         <v>29</v>
       </c>
       <c r="AV4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AW4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AX4" t="n">
         <v>20</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>11-23-2008-09</t>
+          <t>2008-11-23</t>
         </is>
       </c>
     </row>
@@ -1210,157 +1277,157 @@
         <v>13</v>
       </c>
       <c r="E5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G5" t="n">
-        <v>0.385</v>
+        <v>0.462</v>
       </c>
       <c r="H5" t="n">
         <v>48</v>
       </c>
       <c r="I5" t="n">
-        <v>35.8</v>
+        <v>35.7</v>
       </c>
       <c r="J5" t="n">
-        <v>86</v>
+        <v>84.5</v>
       </c>
       <c r="K5" t="n">
-        <v>0.417</v>
+        <v>0.423</v>
       </c>
       <c r="L5" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="M5" t="n">
-        <v>16.4</v>
+        <v>15.4</v>
       </c>
       <c r="N5" t="n">
-        <v>0.343</v>
+        <v>0.35</v>
       </c>
       <c r="O5" t="n">
-        <v>20.2</v>
+        <v>21.3</v>
       </c>
       <c r="P5" t="n">
-        <v>25</v>
+        <v>26.7</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.798</v>
       </c>
       <c r="R5" t="n">
         <v>13.2</v>
       </c>
       <c r="S5" t="n">
-        <v>30.4</v>
+        <v>30.5</v>
       </c>
       <c r="T5" t="n">
-        <v>43.5</v>
+        <v>43.6</v>
       </c>
       <c r="U5" t="n">
-        <v>18.2</v>
+        <v>18.8</v>
       </c>
       <c r="V5" t="n">
-        <v>15.4</v>
+        <v>15.5</v>
       </c>
       <c r="W5" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="X5" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="Y5" t="n">
-        <v>7.3</v>
+        <v>6.9</v>
       </c>
       <c r="Z5" t="n">
-        <v>23.8</v>
+        <v>22.8</v>
       </c>
       <c r="AA5" t="n">
-        <v>21</v>
+        <v>21.7</v>
       </c>
       <c r="AB5" t="n">
-        <v>97.5</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="AC5" t="n">
-        <v>-4.4</v>
+        <v>-2.4</v>
       </c>
       <c r="AD5" t="n">
         <v>9</v>
       </c>
       <c r="AE5" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="AF5" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AG5" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AH5" t="n">
         <v>20</v>
       </c>
       <c r="AI5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AJ5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>28</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>17</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>22</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>16</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>6</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>8</v>
+      </c>
+      <c r="AQ5" t="n">
         <v>4</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>29</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>18</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>17</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>20</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>9</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>17</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>3</v>
       </c>
       <c r="AR5" t="n">
         <v>5</v>
       </c>
       <c r="AS5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AT5" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AU5" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AV5" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AW5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AX5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AY5" t="n">
         <v>30</v>
       </c>
       <c r="AZ5" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="BA5" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="BB5" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="BC5" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="BD5" t="n">
         <v>10</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>11-23-2008-09</t>
+          <t>2008-11-23</t>
         </is>
       </c>
     </row>
@@ -1389,91 +1456,91 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E6" t="n">
         <v>10</v>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G6" t="n">
-        <v>0.833</v>
+        <v>0.769</v>
       </c>
       <c r="H6" t="n">
         <v>48</v>
       </c>
       <c r="I6" t="n">
-        <v>37</v>
+        <v>36.4</v>
       </c>
       <c r="J6" t="n">
-        <v>77.40000000000001</v>
+        <v>76.7</v>
       </c>
       <c r="K6" t="n">
-        <v>0.478</v>
+        <v>0.474</v>
       </c>
       <c r="L6" t="n">
-        <v>7</v>
+        <v>6.7</v>
       </c>
       <c r="M6" t="n">
-        <v>19.5</v>
+        <v>19.2</v>
       </c>
       <c r="N6" t="n">
-        <v>0.359</v>
+        <v>0.349</v>
       </c>
       <c r="O6" t="n">
-        <v>21.6</v>
+        <v>21.8</v>
       </c>
       <c r="P6" t="n">
-        <v>27.3</v>
+        <v>27.7</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.792</v>
+        <v>0.786</v>
       </c>
       <c r="R6" t="n">
-        <v>10.9</v>
+        <v>10.7</v>
       </c>
       <c r="S6" t="n">
-        <v>29.5</v>
+        <v>29.8</v>
       </c>
       <c r="T6" t="n">
-        <v>40.4</v>
+        <v>40.5</v>
       </c>
       <c r="U6" t="n">
-        <v>20.3</v>
+        <v>20</v>
       </c>
       <c r="V6" t="n">
-        <v>12.6</v>
+        <v>13.3</v>
       </c>
       <c r="W6" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="X6" t="n">
-        <v>6.1</v>
+        <v>5.8</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="Z6" t="n">
-        <v>21.1</v>
+        <v>21.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>21.8</v>
+        <v>22.3</v>
       </c>
       <c r="AB6" t="n">
-        <v>102.6</v>
+        <v>101.2</v>
       </c>
       <c r="AC6" t="n">
-        <v>9.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD6" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="AE6" t="n">
         <v>2</v>
       </c>
       <c r="AF6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG6" t="n">
         <v>3</v>
@@ -1482,13 +1549,13 @@
         <v>20</v>
       </c>
       <c r="AI6" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AJ6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AK6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL6" t="n">
         <v>10</v>
@@ -1497,46 +1564,46 @@
         <v>8</v>
       </c>
       <c r="AN6" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AO6" t="n">
         <v>4</v>
       </c>
       <c r="AP6" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AQ6" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AR6" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AS6" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AT6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AU6" t="n">
+        <v>19</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW6" t="n">
         <v>15</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>3</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>17</v>
       </c>
       <c r="AX6" t="n">
         <v>7</v>
       </c>
       <c r="AY6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AZ6" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="BA6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BB6" t="n">
         <v>4</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>11-23-2008-09</t>
+          <t>2008-11-23</t>
         </is>
       </c>
     </row>
@@ -1652,34 +1719,34 @@
         <v>9</v>
       </c>
       <c r="AE7" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AF7" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AG7" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AH7" t="n">
         <v>9</v>
       </c>
       <c r="AI7" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AJ7" t="n">
         <v>7</v>
       </c>
       <c r="AK7" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AM7" t="n">
         <v>11</v>
       </c>
       <c r="AN7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AO7" t="n">
         <v>17</v>
@@ -1688,7 +1755,7 @@
         <v>19</v>
       </c>
       <c r="AQ7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AR7" t="n">
         <v>7</v>
@@ -1706,10 +1773,10 @@
         <v>14</v>
       </c>
       <c r="AW7" t="n">
+        <v>15</v>
+      </c>
+      <c r="AX7" t="n">
         <v>14</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>13</v>
       </c>
       <c r="AY7" t="n">
         <v>6</v>
@@ -1721,10 +1788,10 @@
         <v>25</v>
       </c>
       <c r="BB7" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BC7" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BD7" t="n">
         <v>10</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>11-23-2008-09</t>
+          <t>2008-11-23</t>
         </is>
       </c>
     </row>
@@ -1753,136 +1820,136 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F8" t="n">
         <v>5</v>
       </c>
       <c r="G8" t="n">
-        <v>0.643</v>
+        <v>0.615</v>
       </c>
       <c r="H8" t="n">
         <v>48.4</v>
       </c>
       <c r="I8" t="n">
-        <v>34.9</v>
+        <v>34.5</v>
       </c>
       <c r="J8" t="n">
-        <v>77.90000000000001</v>
+        <v>78.2</v>
       </c>
       <c r="K8" t="n">
-        <v>0.448</v>
+        <v>0.441</v>
       </c>
       <c r="L8" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="M8" t="n">
-        <v>16</v>
+        <v>16.1</v>
       </c>
       <c r="N8" t="n">
-        <v>0.313</v>
+        <v>0.316</v>
       </c>
       <c r="O8" t="n">
-        <v>24.6</v>
+        <v>24.2</v>
       </c>
       <c r="P8" t="n">
-        <v>31.9</v>
+        <v>31.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.772</v>
+        <v>0.778</v>
       </c>
       <c r="R8" t="n">
-        <v>10</v>
+        <v>10.2</v>
       </c>
       <c r="S8" t="n">
-        <v>31.7</v>
+        <v>31.6</v>
       </c>
       <c r="T8" t="n">
-        <v>41.7</v>
+        <v>41.8</v>
       </c>
       <c r="U8" t="n">
-        <v>22.3</v>
+        <v>21.6</v>
       </c>
       <c r="V8" t="n">
-        <v>16.1</v>
+        <v>16.3</v>
       </c>
       <c r="W8" t="n">
         <v>9.5</v>
       </c>
       <c r="X8" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="Y8" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>22.9</v>
+        <v>23</v>
       </c>
       <c r="AA8" t="n">
-        <v>25.4</v>
+        <v>25</v>
       </c>
       <c r="AB8" t="n">
-        <v>99.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="AE8" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AF8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG8" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AH8" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="AI8" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AJ8" t="n">
         <v>22</v>
       </c>
       <c r="AK8" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AL8" t="n">
         <v>22</v>
       </c>
       <c r="AM8" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AN8" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AO8" t="n">
         <v>1</v>
       </c>
       <c r="AP8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AQ8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AR8" t="n">
         <v>25</v>
       </c>
       <c r="AS8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AT8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AU8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AV8" t="n">
         <v>23</v>
@@ -1891,22 +1958,22 @@
         <v>2</v>
       </c>
       <c r="AX8" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AY8" t="n">
         <v>28</v>
       </c>
       <c r="AZ8" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BA8" t="n">
         <v>2</v>
       </c>
       <c r="BB8" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BC8" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="BD8" t="n">
         <v>10</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>11-23-2008-09</t>
+          <t>2008-11-23</t>
         </is>
       </c>
     </row>
@@ -1935,64 +2002,64 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E9" t="n">
         <v>8</v>
       </c>
       <c r="F9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G9" t="n">
-        <v>0.615</v>
+        <v>0.667</v>
       </c>
       <c r="H9" t="n">
         <v>48</v>
       </c>
       <c r="I9" t="n">
-        <v>34.8</v>
+        <v>35.3</v>
       </c>
       <c r="J9" t="n">
-        <v>79.09999999999999</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>0.441</v>
+        <v>0.447</v>
       </c>
       <c r="L9" t="n">
         <v>5.8</v>
       </c>
       <c r="M9" t="n">
-        <v>14.9</v>
+        <v>15</v>
       </c>
       <c r="N9" t="n">
-        <v>0.387</v>
+        <v>0.389</v>
       </c>
       <c r="O9" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="P9" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.788</v>
+      </c>
+      <c r="R9" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="S9" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="T9" t="n">
+        <v>41.8</v>
+      </c>
+      <c r="U9" t="n">
         <v>20.3</v>
       </c>
-      <c r="P9" t="n">
-        <v>26</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0.781</v>
-      </c>
-      <c r="R9" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="S9" t="n">
-        <v>29.8</v>
-      </c>
-      <c r="T9" t="n">
-        <v>41.4</v>
-      </c>
-      <c r="U9" t="n">
-        <v>20.4</v>
-      </c>
       <c r="V9" t="n">
-        <v>13.3</v>
+        <v>13.5</v>
       </c>
       <c r="W9" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="X9" t="n">
         <v>5.2</v>
@@ -2001,40 +2068,40 @@
         <v>4.6</v>
       </c>
       <c r="Z9" t="n">
-        <v>21.9</v>
+        <v>22.3</v>
       </c>
       <c r="AA9" t="n">
-        <v>21.9</v>
+        <v>22.3</v>
       </c>
       <c r="AB9" t="n">
-        <v>95.8</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="AC9" t="n">
-        <v>-0.8</v>
+        <v>1.3</v>
       </c>
       <c r="AD9" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="AE9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AF9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG9" t="n">
         <v>5</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>9</v>
       </c>
       <c r="AH9" t="n">
         <v>20</v>
       </c>
       <c r="AI9" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="AJ9" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AK9" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AL9" t="n">
         <v>15</v>
@@ -2046,49 +2113,49 @@
         <v>5</v>
       </c>
       <c r="AO9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AP9" t="n">
         <v>11</v>
       </c>
       <c r="AQ9" t="n">
+        <v>8</v>
+      </c>
+      <c r="AR9" t="n">
         <v>9</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>11</v>
       </c>
       <c r="AS9" t="n">
         <v>18</v>
       </c>
       <c r="AT9" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AU9" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AV9" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AW9" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AX9" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AY9" t="n">
         <v>12</v>
       </c>
       <c r="AZ9" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB9" t="n">
         <v>18</v>
       </c>
-      <c r="BA9" t="n">
-        <v>10</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>22</v>
-      </c>
       <c r="BC9" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="BD9" t="n">
         <v>10</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>11-23-2008-09</t>
+          <t>2008-11-23</t>
         </is>
       </c>
     </row>
@@ -2117,91 +2184,91 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E10" t="n">
         <v>5</v>
       </c>
       <c r="F10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G10" t="n">
-        <v>0.385</v>
+        <v>0.417</v>
       </c>
       <c r="H10" t="n">
         <v>48.8</v>
       </c>
       <c r="I10" t="n">
-        <v>38.2</v>
+        <v>38.5</v>
       </c>
       <c r="J10" t="n">
-        <v>86.59999999999999</v>
+        <v>87.3</v>
       </c>
       <c r="K10" t="n">
-        <v>0.44</v>
+        <v>0.441</v>
       </c>
       <c r="L10" t="n">
         <v>5.3</v>
       </c>
       <c r="M10" t="n">
-        <v>17.5</v>
+        <v>17.4</v>
       </c>
       <c r="N10" t="n">
-        <v>0.304</v>
+        <v>0.301</v>
       </c>
       <c r="O10" t="n">
-        <v>21.9</v>
+        <v>23.2</v>
       </c>
       <c r="P10" t="n">
-        <v>30.4</v>
+        <v>31.8</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.722</v>
+        <v>0.728</v>
       </c>
       <c r="R10" t="n">
-        <v>14</v>
+        <v>14.3</v>
       </c>
       <c r="S10" t="n">
-        <v>29.9</v>
+        <v>30.2</v>
       </c>
       <c r="T10" t="n">
-        <v>43.9</v>
+        <v>44.4</v>
       </c>
       <c r="U10" t="n">
         <v>19.7</v>
       </c>
       <c r="V10" t="n">
-        <v>15.2</v>
+        <v>15</v>
       </c>
       <c r="W10" t="n">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="X10" t="n">
-        <v>6.9</v>
+        <v>6.4</v>
       </c>
       <c r="Y10" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="Z10" t="n">
-        <v>21.5</v>
+        <v>22.1</v>
       </c>
       <c r="AA10" t="n">
-        <v>25.7</v>
+        <v>26.4</v>
       </c>
       <c r="AB10" t="n">
-        <v>103.5</v>
+        <v>105.4</v>
       </c>
       <c r="AC10" t="n">
-        <v>-1.2</v>
+        <v>-0.7</v>
       </c>
       <c r="AD10" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="AE10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AF10" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AG10" t="n">
         <v>22</v>
@@ -2210,28 +2277,28 @@
         <v>5</v>
       </c>
       <c r="AI10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AJ10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AK10" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AL10" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AM10" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AN10" t="n">
         <v>28</v>
       </c>
       <c r="AO10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AP10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AQ10" t="n">
         <v>29</v>
@@ -2240,7 +2307,7 @@
         <v>2</v>
       </c>
       <c r="AS10" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AT10" t="n">
         <v>6</v>
@@ -2252,25 +2319,25 @@
         <v>17</v>
       </c>
       <c r="AW10" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AX10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AY10" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AZ10" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BA10" t="n">
         <v>1</v>
       </c>
       <c r="BB10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BC10" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BD10" t="n">
         <v>10</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>11-23-2008-09</t>
+          <t>2008-11-23</t>
         </is>
       </c>
     </row>
@@ -2383,10 +2450,10 @@
         <v>4</v>
       </c>
       <c r="AF11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH11" t="n">
         <v>15</v>
@@ -2395,16 +2462,16 @@
         <v>29</v>
       </c>
       <c r="AJ11" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AK11" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL11" t="n">
         <v>14</v>
       </c>
       <c r="AM11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AN11" t="n">
         <v>19</v>
@@ -2422,7 +2489,7 @@
         <v>22</v>
       </c>
       <c r="AS11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AT11" t="n">
         <v>11</v>
@@ -2431,7 +2498,7 @@
         <v>26</v>
       </c>
       <c r="AV11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW11" t="n">
         <v>20</v>
@@ -2443,7 +2510,7 @@
         <v>18</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BA11" t="n">
         <v>23</v>
@@ -2452,7 +2519,7 @@
         <v>25</v>
       </c>
       <c r="BC11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BD11" t="n">
         <v>10</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>11-23-2008-09</t>
+          <t>2008-11-23</t>
         </is>
       </c>
     </row>
@@ -2559,16 +2626,16 @@
         <v>2</v>
       </c>
       <c r="AD12" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE12" t="n">
         <v>22</v>
       </c>
-      <c r="AE12" t="n">
-        <v>21</v>
-      </c>
       <c r="AF12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AG12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AH12" t="n">
         <v>7</v>
@@ -2592,13 +2659,13 @@
         <v>13</v>
       </c>
       <c r="AO12" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AP12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AR12" t="n">
         <v>14</v>
@@ -2607,19 +2674,19 @@
         <v>2</v>
       </c>
       <c r="AT12" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU12" t="n">
         <v>5</v>
       </c>
-      <c r="AU12" t="n">
-        <v>7</v>
-      </c>
       <c r="AV12" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AW12" t="n">
         <v>18</v>
       </c>
       <c r="AX12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AY12" t="n">
         <v>25</v>
@@ -2628,13 +2695,13 @@
         <v>22</v>
       </c>
       <c r="BA12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BB12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BC12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>11-23-2008-09</t>
+          <t>2008-11-23</t>
         </is>
       </c>
     </row>
@@ -2744,7 +2811,7 @@
         <v>9</v>
       </c>
       <c r="AE13" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AF13" t="n">
         <v>29</v>
@@ -2756,7 +2823,7 @@
         <v>9</v>
       </c>
       <c r="AI13" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AJ13" t="n">
         <v>10</v>
@@ -2765,10 +2832,10 @@
         <v>27</v>
       </c>
       <c r="AL13" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AM13" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AN13" t="n">
         <v>27</v>
@@ -2783,31 +2850,31 @@
         <v>25</v>
       </c>
       <c r="AR13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AS13" t="n">
         <v>24</v>
       </c>
       <c r="AT13" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AU13" t="n">
         <v>20</v>
       </c>
       <c r="AV13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AW13" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AX13" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AY13" t="n">
         <v>15</v>
       </c>
       <c r="AZ13" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BA13" t="n">
         <v>26</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>11-23-2008-09</t>
+          <t>2008-11-23</t>
         </is>
       </c>
     </row>
@@ -2860,70 +2927,70 @@
         <v>48</v>
       </c>
       <c r="I14" t="n">
-        <v>39.7</v>
+        <v>39</v>
       </c>
       <c r="J14" t="n">
-        <v>87.09999999999999</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>0.456</v>
+        <v>0.452</v>
       </c>
       <c r="L14" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="M14" t="n">
-        <v>17.7</v>
+        <v>17.4</v>
       </c>
       <c r="N14" t="n">
-        <v>0.379</v>
+        <v>0.382</v>
       </c>
       <c r="O14" t="n">
-        <v>20.6</v>
+        <v>20.2</v>
       </c>
       <c r="P14" t="n">
-        <v>27.4</v>
+        <v>26.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.754</v>
+        <v>0.763</v>
       </c>
       <c r="R14" t="n">
-        <v>13.9</v>
+        <v>13.5</v>
       </c>
       <c r="S14" t="n">
-        <v>32.6</v>
+        <v>33.4</v>
       </c>
       <c r="T14" t="n">
-        <v>46.5</v>
+        <v>46.8</v>
       </c>
       <c r="U14" t="n">
-        <v>22.5</v>
+        <v>21.7</v>
       </c>
       <c r="V14" t="n">
-        <v>13.9</v>
+        <v>13.6</v>
       </c>
       <c r="W14" t="n">
-        <v>10.6</v>
+        <v>10.4</v>
       </c>
       <c r="X14" t="n">
-        <v>6.3</v>
+        <v>6.6</v>
       </c>
       <c r="Y14" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="AA14" t="n">
-        <v>22.4</v>
+        <v>21.8</v>
       </c>
       <c r="AB14" t="n">
-        <v>106.8</v>
+        <v>104.8</v>
       </c>
       <c r="AC14" t="n">
-        <v>12.6</v>
+        <v>13.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AE14" t="n">
         <v>2</v>
@@ -2941,7 +3008,7 @@
         <v>1</v>
       </c>
       <c r="AJ14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AK14" t="n">
         <v>11</v>
@@ -2950,52 +3017,52 @@
         <v>11</v>
       </c>
       <c r="AM14" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AN14" t="n">
+        <v>8</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>10</v>
+      </c>
+      <c r="AP14" t="n">
         <v>9</v>
       </c>
-      <c r="AO14" t="n">
-        <v>7</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>6</v>
-      </c>
       <c r="AQ14" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AR14" t="n">
         <v>4</v>
       </c>
       <c r="AS14" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AT14" t="n">
         <v>3</v>
       </c>
       <c r="AU14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV14" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AW14" t="n">
         <v>1</v>
       </c>
       <c r="AX14" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AY14" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="AZ14" t="n">
         <v>9</v>
       </c>
       <c r="BA14" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="BB14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BC14" t="n">
         <v>1</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>11-23-2008-09</t>
+          <t>2008-11-23</t>
         </is>
       </c>
     </row>
@@ -3120,19 +3187,19 @@
         <v>9</v>
       </c>
       <c r="AI15" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AJ15" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AK15" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL15" t="n">
         <v>25</v>
       </c>
       <c r="AM15" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AN15" t="n">
         <v>22</v>
@@ -3147,10 +3214,10 @@
         <v>10</v>
       </c>
       <c r="AR15" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AS15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AT15" t="n">
         <v>13</v>
@@ -3174,13 +3241,13 @@
         <v>24</v>
       </c>
       <c r="BA15" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="BB15" t="n">
         <v>26</v>
       </c>
       <c r="BC15" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BD15" t="n">
         <v>10</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>11-23-2008-09</t>
+          <t>2008-11-23</t>
         </is>
       </c>
     </row>
@@ -3293,7 +3360,7 @@
         <v>12</v>
       </c>
       <c r="AF16" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AG16" t="n">
         <v>13</v>
@@ -3302,25 +3369,25 @@
         <v>20</v>
       </c>
       <c r="AI16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AJ16" t="n">
         <v>14</v>
       </c>
       <c r="AK16" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AL16" t="n">
         <v>6</v>
       </c>
       <c r="AM16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AN16" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AO16" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AP16" t="n">
         <v>18</v>
@@ -3329,25 +3396,25 @@
         <v>24</v>
       </c>
       <c r="AR16" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AS16" t="n">
         <v>25</v>
       </c>
       <c r="AT16" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AU16" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AV16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW16" t="n">
         <v>6</v>
       </c>
       <c r="AX16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AY16" t="n">
         <v>4</v>
@@ -3359,7 +3426,7 @@
         <v>20</v>
       </c>
       <c r="BB16" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="BC16" t="n">
         <v>5</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>11-23-2008-09</t>
+          <t>2008-11-23</t>
         </is>
       </c>
     </row>
@@ -3391,43 +3458,43 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E17" t="n">
         <v>7</v>
       </c>
       <c r="F17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G17" t="n">
-        <v>0.5</v>
+        <v>0.467</v>
       </c>
       <c r="H17" t="n">
-        <v>49.1</v>
+        <v>49</v>
       </c>
       <c r="I17" t="n">
-        <v>34.9</v>
+        <v>35</v>
       </c>
       <c r="J17" t="n">
-        <v>82.09999999999999</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="K17" t="n">
-        <v>0.424</v>
+        <v>0.428</v>
       </c>
       <c r="L17" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="M17" t="n">
         <v>14.2</v>
       </c>
       <c r="N17" t="n">
-        <v>0.362</v>
+        <v>0.366</v>
       </c>
       <c r="O17" t="n">
-        <v>20.2</v>
+        <v>19.9</v>
       </c>
       <c r="P17" t="n">
-        <v>26.9</v>
+        <v>26.4</v>
       </c>
       <c r="Q17" t="n">
         <v>0.753</v>
@@ -3436,76 +3503,76 @@
         <v>13.9</v>
       </c>
       <c r="S17" t="n">
-        <v>32.1</v>
+        <v>31.2</v>
       </c>
       <c r="T17" t="n">
-        <v>46</v>
+        <v>45.1</v>
       </c>
       <c r="U17" t="n">
         <v>20.3</v>
       </c>
       <c r="V17" t="n">
-        <v>16.5</v>
+        <v>16.7</v>
       </c>
       <c r="W17" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="X17" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="Y17" t="n">
         <v>5.6</v>
       </c>
       <c r="Z17" t="n">
-        <v>25.1</v>
+        <v>25.4</v>
       </c>
       <c r="AA17" t="n">
-        <v>24.6</v>
+        <v>24.2</v>
       </c>
       <c r="AB17" t="n">
         <v>95.09999999999999</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.2</v>
+        <v>-0.7</v>
       </c>
       <c r="AD17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE17" t="n">
         <v>12</v>
       </c>
       <c r="AF17" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="AG17" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AH17" t="n">
         <v>2</v>
       </c>
       <c r="AI17" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AJ17" t="n">
         <v>11</v>
       </c>
       <c r="AK17" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL17" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AM17" t="n">
         <v>27</v>
       </c>
       <c r="AN17" t="n">
+        <v>11</v>
+      </c>
+      <c r="AO17" t="n">
         <v>12</v>
       </c>
-      <c r="AO17" t="n">
+      <c r="AP17" t="n">
         <v>10</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>9</v>
       </c>
       <c r="AQ17" t="n">
         <v>20</v>
@@ -3514,25 +3581,25 @@
         <v>3</v>
       </c>
       <c r="AS17" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="AT17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AU17" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AV17" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AW17" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AX17" t="n">
         <v>27</v>
       </c>
       <c r="AY17" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AZ17" t="n">
         <v>29</v>
@@ -3544,7 +3611,7 @@
         <v>23</v>
       </c>
       <c r="BC17" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="BD17" t="n">
         <v>10</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>11-23-2008-09</t>
+          <t>2008-11-23</t>
         </is>
       </c>
     </row>
@@ -3573,64 +3640,64 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F18" t="n">
         <v>9</v>
       </c>
       <c r="G18" t="n">
-        <v>0.25</v>
+        <v>0.182</v>
       </c>
       <c r="H18" t="n">
-        <v>49.3</v>
+        <v>49.4</v>
       </c>
       <c r="I18" t="n">
-        <v>37</v>
+        <v>36.4</v>
       </c>
       <c r="J18" t="n">
-        <v>85.2</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="K18" t="n">
-        <v>0.434</v>
+        <v>0.426</v>
       </c>
       <c r="L18" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="M18" t="n">
-        <v>14.3</v>
+        <v>14.6</v>
       </c>
       <c r="N18" t="n">
-        <v>0.308</v>
+        <v>0.286</v>
       </c>
       <c r="O18" t="n">
-        <v>18.1</v>
+        <v>18.7</v>
       </c>
       <c r="P18" t="n">
-        <v>22.6</v>
+        <v>23.4</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.801</v>
+        <v>0.802</v>
       </c>
       <c r="R18" t="n">
-        <v>10.9</v>
+        <v>11.3</v>
       </c>
       <c r="S18" t="n">
-        <v>29.8</v>
+        <v>29</v>
       </c>
       <c r="T18" t="n">
-        <v>40.7</v>
+        <v>40.3</v>
       </c>
       <c r="U18" t="n">
-        <v>24.2</v>
+        <v>23.5</v>
       </c>
       <c r="V18" t="n">
         <v>12.9</v>
       </c>
       <c r="W18" t="n">
-        <v>5.9</v>
+        <v>6.1</v>
       </c>
       <c r="X18" t="n">
         <v>4.5</v>
@@ -3639,94 +3706,94 @@
         <v>5.8</v>
       </c>
       <c r="Z18" t="n">
-        <v>22.9</v>
+        <v>23.5</v>
       </c>
       <c r="AA18" t="n">
-        <v>21.1</v>
+        <v>21.5</v>
       </c>
       <c r="AB18" t="n">
-        <v>96.5</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="AC18" t="n">
-        <v>-2.5</v>
+        <v>-5.1</v>
       </c>
       <c r="AD18" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="AE18" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AF18" t="n">
         <v>24</v>
       </c>
       <c r="AG18" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AH18" t="n">
         <v>1</v>
       </c>
       <c r="AI18" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AJ18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AK18" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AL18" t="n">
         <v>28</v>
       </c>
       <c r="AM18" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AN18" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AO18" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AP18" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AQ18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AR18" t="n">
         <v>16</v>
       </c>
       <c r="AS18" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AT18" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AU18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW18" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AX18" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AY18" t="n">
         <v>23</v>
       </c>
       <c r="AZ18" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BA18" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BB18" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="BC18" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="BD18" t="n">
         <v>10</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>11-23-2008-09</t>
+          <t>2008-11-23</t>
         </is>
       </c>
     </row>
@@ -3833,22 +3900,22 @@
         <v>-3.3</v>
       </c>
       <c r="AD19" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AE19" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AF19" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AG19" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AH19" t="n">
         <v>7</v>
       </c>
       <c r="AI19" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AJ19" t="n">
         <v>15</v>
@@ -3866,13 +3933,13 @@
         <v>6</v>
       </c>
       <c r="AO19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AP19" t="n">
         <v>5</v>
       </c>
       <c r="AQ19" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AR19" t="n">
         <v>13</v>
@@ -3884,10 +3951,10 @@
         <v>17</v>
       </c>
       <c r="AU19" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AV19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AW19" t="n">
         <v>24</v>
@@ -3905,7 +3972,7 @@
         <v>13</v>
       </c>
       <c r="BB19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BC19" t="n">
         <v>23</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>11-23-2008-09</t>
+          <t>2008-11-23</t>
         </is>
       </c>
     </row>
@@ -4015,28 +4082,28 @@
         <v>3.9</v>
       </c>
       <c r="AD20" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AE20" t="n">
         <v>12</v>
       </c>
       <c r="AF20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG20" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH20" t="n">
         <v>30</v>
       </c>
       <c r="AI20" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AJ20" t="n">
         <v>27</v>
       </c>
       <c r="AK20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AL20" t="n">
         <v>8</v>
@@ -4048,13 +4115,13 @@
         <v>7</v>
       </c>
       <c r="AO20" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AP20" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AR20" t="n">
         <v>27</v>
@@ -4066,10 +4133,10 @@
         <v>30</v>
       </c>
       <c r="AU20" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AV20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW20" t="n">
         <v>5</v>
@@ -4078,19 +4145,19 @@
         <v>26</v>
       </c>
       <c r="AY20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AZ20" t="n">
         <v>12</v>
       </c>
       <c r="BA20" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BB20" t="n">
         <v>20</v>
       </c>
       <c r="BC20" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BD20" t="n">
         <v>10</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>11-23-2008-09</t>
+          <t>2008-11-23</t>
         </is>
       </c>
     </row>
@@ -4203,7 +4270,7 @@
         <v>12</v>
       </c>
       <c r="AF21" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AG21" t="n">
         <v>13</v>
@@ -4230,19 +4297,19 @@
         <v>10</v>
       </c>
       <c r="AO21" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AP21" t="n">
         <v>27</v>
       </c>
       <c r="AQ21" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AR21" t="n">
         <v>24</v>
       </c>
       <c r="AS21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AT21" t="n">
         <v>12</v>
@@ -4272,7 +4339,7 @@
         <v>2</v>
       </c>
       <c r="BC21" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BD21" t="n">
         <v>10</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>11-23-2008-09</t>
+          <t>2008-11-23</t>
         </is>
       </c>
     </row>
@@ -4394,7 +4461,7 @@
         <v>20</v>
       </c>
       <c r="AI22" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AJ22" t="n">
         <v>9</v>
@@ -4409,25 +4476,25 @@
         <v>30</v>
       </c>
       <c r="AN22" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AO22" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AP22" t="n">
         <v>20</v>
       </c>
       <c r="AQ22" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AR22" t="n">
+        <v>10</v>
+      </c>
+      <c r="AS22" t="n">
         <v>9</v>
       </c>
-      <c r="AS22" t="n">
-        <v>10</v>
-      </c>
       <c r="AT22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AU22" t="n">
         <v>27</v>
@@ -4445,7 +4512,7 @@
         <v>27</v>
       </c>
       <c r="AZ22" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BA22" t="n">
         <v>27</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>11-23-2008-09</t>
+          <t>2008-11-23</t>
         </is>
       </c>
     </row>
@@ -4576,7 +4643,7 @@
         <v>9</v>
       </c>
       <c r="AI23" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AJ23" t="n">
         <v>13</v>
@@ -4591,10 +4658,10 @@
         <v>2</v>
       </c>
       <c r="AN23" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AO23" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AP23" t="n">
         <v>4</v>
@@ -4603,10 +4670,10 @@
         <v>30</v>
       </c>
       <c r="AR23" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AS23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AT23" t="n">
         <v>7</v>
@@ -4624,16 +4691,16 @@
         <v>1</v>
       </c>
       <c r="AY23" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB23" t="n">
         <v>8</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>7</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>10</v>
       </c>
       <c r="BC23" t="n">
         <v>4</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>11-23-2008-09</t>
+          <t>2008-11-23</t>
         </is>
       </c>
     </row>
@@ -4665,16 +4732,16 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E24" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F24" t="n">
         <v>6</v>
       </c>
       <c r="G24" t="n">
-        <v>0.538</v>
+        <v>0.5</v>
       </c>
       <c r="H24" t="n">
         <v>48</v>
@@ -4683,76 +4750,76 @@
         <v>37.5</v>
       </c>
       <c r="J24" t="n">
-        <v>85.09999999999999</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="K24" t="n">
-        <v>0.44</v>
+        <v>0.444</v>
       </c>
       <c r="L24" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="M24" t="n">
-        <v>12.4</v>
+        <v>12.2</v>
       </c>
       <c r="N24" t="n">
-        <v>0.36</v>
+        <v>0.356</v>
       </c>
       <c r="O24" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="P24" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0.739</v>
+      </c>
+      <c r="R24" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="S24" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="T24" t="n">
+        <v>47.8</v>
+      </c>
+      <c r="U24" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="V24" t="n">
         <v>16.6</v>
-      </c>
-      <c r="P24" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="R24" t="n">
-        <v>15</v>
-      </c>
-      <c r="S24" t="n">
-        <v>33.2</v>
-      </c>
-      <c r="T24" t="n">
-        <v>48.2</v>
-      </c>
-      <c r="U24" t="n">
-        <v>20.3</v>
-      </c>
-      <c r="V24" t="n">
-        <v>16.8</v>
       </c>
       <c r="W24" t="n">
         <v>6.8</v>
       </c>
       <c r="X24" t="n">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="Y24" t="n">
-        <v>5.9</v>
+        <v>5.3</v>
       </c>
       <c r="Z24" t="n">
-        <v>18.6</v>
+        <v>18.8</v>
       </c>
       <c r="AA24" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>96.59999999999999</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AD24" t="n">
         <v>19</v>
       </c>
-      <c r="AB24" t="n">
-        <v>96</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>9</v>
-      </c>
       <c r="AE24" t="n">
+        <v>16</v>
+      </c>
+      <c r="AF24" t="n">
         <v>12</v>
       </c>
-      <c r="AF24" t="n">
-        <v>13</v>
-      </c>
       <c r="AG24" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AH24" t="n">
         <v>20</v>
@@ -4764,7 +4831,7 @@
         <v>6</v>
       </c>
       <c r="AK24" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AL24" t="n">
         <v>27</v>
@@ -4776,10 +4843,10 @@
         <v>14</v>
       </c>
       <c r="AO24" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AP24" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AQ24" t="n">
         <v>26</v>
@@ -4788,34 +4855,34 @@
         <v>1</v>
       </c>
       <c r="AS24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AT24" t="n">
         <v>1</v>
       </c>
       <c r="AU24" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AV24" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AW24" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AX24" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AY24" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="AZ24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BA24" t="n">
         <v>28</v>
       </c>
       <c r="BB24" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="BC24" t="n">
         <v>9</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>11-23-2008-09</t>
+          <t>2008-11-23</t>
         </is>
       </c>
     </row>
@@ -4931,16 +4998,16 @@
         <v>4</v>
       </c>
       <c r="AF25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH25" t="n">
         <v>15</v>
       </c>
       <c r="AI25" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AJ25" t="n">
         <v>30</v>
@@ -4952,13 +5019,13 @@
         <v>13</v>
       </c>
       <c r="AM25" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AN25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AO25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AP25" t="n">
         <v>7</v>
@@ -4970,37 +5037,37 @@
         <v>29</v>
       </c>
       <c r="AS25" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AT25" t="n">
         <v>22</v>
       </c>
       <c r="AU25" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AV25" t="n">
+        <v>29</v>
+      </c>
+      <c r="AW25" t="n">
         <v>28</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>29</v>
       </c>
       <c r="AX25" t="n">
         <v>17</v>
       </c>
       <c r="AY25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AZ25" t="n">
         <v>6</v>
       </c>
       <c r="BA25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BB25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BC25" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BD25" t="n">
         <v>10</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>11-23-2008-09</t>
+          <t>2008-11-23</t>
         </is>
       </c>
     </row>
@@ -5029,106 +5096,106 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E26" t="n">
         <v>8</v>
       </c>
       <c r="F26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G26" t="n">
-        <v>0.615</v>
+        <v>0.571</v>
       </c>
       <c r="H26" t="n">
         <v>48.4</v>
       </c>
       <c r="I26" t="n">
-        <v>36.6</v>
+        <v>36.1</v>
       </c>
       <c r="J26" t="n">
-        <v>79.5</v>
+        <v>79.8</v>
       </c>
       <c r="K26" t="n">
-        <v>0.461</v>
+        <v>0.452</v>
       </c>
       <c r="L26" t="n">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="M26" t="n">
-        <v>20.9</v>
+        <v>21.1</v>
       </c>
       <c r="N26" t="n">
         <v>0.419</v>
       </c>
       <c r="O26" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="P26" t="n">
-        <v>23.4</v>
+        <v>22.7</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.773</v>
+        <v>0.764</v>
       </c>
       <c r="R26" t="n">
         <v>12.6</v>
       </c>
       <c r="S26" t="n">
-        <v>26.5</v>
+        <v>26.9</v>
       </c>
       <c r="T26" t="n">
-        <v>39.2</v>
+        <v>39.5</v>
       </c>
       <c r="U26" t="n">
-        <v>20.8</v>
+        <v>20.6</v>
       </c>
       <c r="V26" t="n">
-        <v>12.3</v>
+        <v>12.4</v>
       </c>
       <c r="W26" t="n">
         <v>7.5</v>
       </c>
       <c r="X26" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="Y26" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="Z26" t="n">
-        <v>21.5</v>
+        <v>21.2</v>
       </c>
       <c r="AA26" t="n">
-        <v>20.7</v>
+        <v>20.4</v>
       </c>
       <c r="AB26" t="n">
-        <v>100.1</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="AC26" t="n">
-        <v>4</v>
+        <v>2.3</v>
       </c>
       <c r="AD26" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="AE26" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AF26" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="AG26" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AH26" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="AI26" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AJ26" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AK26" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AL26" t="n">
         <v>3</v>
@@ -5140,13 +5207,13 @@
         <v>2</v>
       </c>
       <c r="AO26" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AP26" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AQ26" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="AR26" t="n">
         <v>6</v>
@@ -5170,19 +5237,19 @@
         <v>11</v>
       </c>
       <c r="AY26" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AZ26" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA26" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="BB26" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="BC26" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="BD26" t="n">
         <v>10</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>11-23-2008-09</t>
+          <t>2008-11-23</t>
         </is>
       </c>
     </row>
@@ -5211,103 +5278,103 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E27" t="n">
         <v>5</v>
       </c>
       <c r="F27" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G27" t="n">
-        <v>0.333</v>
+        <v>0.357</v>
       </c>
       <c r="H27" t="n">
-        <v>48.3</v>
+        <v>48.4</v>
       </c>
       <c r="I27" t="n">
-        <v>38.6</v>
+        <v>38</v>
       </c>
       <c r="J27" t="n">
-        <v>79.3</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="K27" t="n">
-        <v>0.487</v>
+        <v>0.483</v>
       </c>
       <c r="L27" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="M27" t="n">
-        <v>15.9</v>
+        <v>15.6</v>
       </c>
       <c r="N27" t="n">
-        <v>0.297</v>
+        <v>0.306</v>
       </c>
       <c r="O27" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="P27" t="n">
-        <v>21.5</v>
+        <v>22.1</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.789</v>
+        <v>0.79</v>
       </c>
       <c r="R27" t="n">
-        <v>9.300000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="S27" t="n">
         <v>28.4</v>
       </c>
       <c r="T27" t="n">
-        <v>37.7</v>
+        <v>37.8</v>
       </c>
       <c r="U27" t="n">
-        <v>21</v>
+        <v>20.4</v>
       </c>
       <c r="V27" t="n">
         <v>15.9</v>
       </c>
       <c r="W27" t="n">
-        <v>6.8</v>
+        <v>6.5</v>
       </c>
       <c r="X27" t="n">
         <v>4.1</v>
       </c>
       <c r="Y27" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="Z27" t="n">
-        <v>22.7</v>
+        <v>22.6</v>
       </c>
       <c r="AA27" t="n">
-        <v>20.4</v>
+        <v>20.7</v>
       </c>
       <c r="AB27" t="n">
-        <v>98.90000000000001</v>
+        <v>98.3</v>
       </c>
       <c r="AC27" t="n">
-        <v>-6</v>
+        <v>-5.7</v>
       </c>
       <c r="AD27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE27" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AF27" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AG27" t="n">
         <v>24</v>
       </c>
       <c r="AH27" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="AI27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AJ27" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AK27" t="n">
         <v>2</v>
@@ -5319,49 +5386,49 @@
         <v>21</v>
       </c>
       <c r="AN27" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AO27" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AP27" t="n">
         <v>28</v>
       </c>
       <c r="AQ27" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AR27" t="n">
         <v>26</v>
       </c>
       <c r="AS27" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AT27" t="n">
         <v>28</v>
       </c>
       <c r="AU27" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AV27" t="n">
         <v>22</v>
       </c>
       <c r="AW27" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AX27" t="n">
         <v>25</v>
       </c>
       <c r="AY27" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AZ27" t="n">
         <v>23</v>
       </c>
       <c r="BA27" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="BB27" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="BC27" t="n">
         <v>27</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>11-23-2008-09</t>
+          <t>2008-11-23</t>
         </is>
       </c>
     </row>
@@ -5471,28 +5538,28 @@
         <v>-0.4</v>
       </c>
       <c r="AD28" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AE28" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AF28" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AG28" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AH28" t="n">
         <v>3</v>
       </c>
       <c r="AI28" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AJ28" t="n">
         <v>24</v>
       </c>
       <c r="AK28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AL28" t="n">
         <v>5</v>
@@ -5516,13 +5583,13 @@
         <v>30</v>
       </c>
       <c r="AS28" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AT28" t="n">
         <v>27</v>
       </c>
       <c r="AU28" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AV28" t="n">
         <v>2</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>11-23-2008-09</t>
+          <t>2008-11-23</t>
         </is>
       </c>
     </row>
@@ -5575,121 +5642,121 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E29" t="n">
         <v>6</v>
       </c>
       <c r="F29" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G29" t="n">
-        <v>0.462</v>
+        <v>0.5</v>
       </c>
       <c r="H29" t="n">
         <v>48.8</v>
       </c>
       <c r="I29" t="n">
-        <v>35.3</v>
+        <v>35.7</v>
       </c>
       <c r="J29" t="n">
-        <v>77</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="K29" t="n">
-        <v>0.459</v>
+        <v>0.46</v>
       </c>
       <c r="L29" t="n">
         <v>6.6</v>
       </c>
       <c r="M29" t="n">
-        <v>15.9</v>
+        <v>16</v>
       </c>
       <c r="N29" t="n">
-        <v>0.415</v>
+        <v>0.411</v>
       </c>
       <c r="O29" t="n">
-        <v>21.5</v>
+        <v>20.4</v>
       </c>
       <c r="P29" t="n">
-        <v>25.7</v>
+        <v>24.8</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.835</v>
+        <v>0.825</v>
       </c>
       <c r="R29" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="S29" t="n">
-        <v>30.3</v>
+        <v>30.9</v>
       </c>
       <c r="T29" t="n">
-        <v>39.1</v>
+        <v>39.8</v>
       </c>
       <c r="U29" t="n">
-        <v>22.9</v>
+        <v>23.3</v>
       </c>
       <c r="V29" t="n">
         <v>14.9</v>
       </c>
       <c r="W29" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="X29" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>98.3</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>16</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>16</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>25</v>
+      </c>
+      <c r="AK29" t="n">
         <v>6</v>
-      </c>
-      <c r="X29" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>98.7</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>9</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>17</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>18</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>19</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>4</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>19</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>26</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>9</v>
       </c>
       <c r="AL29" t="n">
         <v>12</v>
       </c>
       <c r="AM29" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AN29" t="n">
         <v>3</v>
       </c>
       <c r="AO29" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AP29" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AQ29" t="n">
         <v>1</v>
@@ -5698,10 +5765,10 @@
         <v>28</v>
       </c>
       <c r="AS29" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AT29" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AU29" t="n">
         <v>4</v>
@@ -5710,25 +5777,25 @@
         <v>16</v>
       </c>
       <c r="AW29" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AX29" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AY29" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AZ29" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BA29" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BB29" t="n">
         <v>13</v>
       </c>
       <c r="BC29" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BD29" t="n">
         <v>10</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>11-23-2008-09</t>
+          <t>2008-11-23</t>
         </is>
       </c>
     </row>
@@ -5841,10 +5908,10 @@
         <v>4</v>
       </c>
       <c r="AF30" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG30" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH30" t="n">
         <v>20</v>
@@ -5853,10 +5920,10 @@
         <v>7</v>
       </c>
       <c r="AJ30" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AK30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AL30" t="n">
         <v>29</v>
@@ -5865,40 +5932,40 @@
         <v>29</v>
       </c>
       <c r="AN30" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AO30" t="n">
         <v>15</v>
       </c>
       <c r="AP30" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AQ30" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AR30" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AS30" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AT30" t="n">
         <v>18</v>
       </c>
       <c r="AU30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV30" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AW30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AX30" t="n">
         <v>17</v>
       </c>
       <c r="AY30" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AZ30" t="n">
         <v>20</v>
@@ -5910,7 +5977,7 @@
         <v>15</v>
       </c>
       <c r="BC30" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BD30" t="n">
         <v>10</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>11-23-2008-09</t>
+          <t>2008-11-23</t>
         </is>
       </c>
     </row>
@@ -6017,13 +6084,13 @@
         <v>-8.800000000000001</v>
       </c>
       <c r="AD31" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AE31" t="n">
         <v>29</v>
       </c>
       <c r="AF31" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AG31" t="n">
         <v>29</v>
@@ -6032,7 +6099,7 @@
         <v>6</v>
       </c>
       <c r="AI31" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AJ31" t="n">
         <v>12</v>
@@ -6053,7 +6120,7 @@
         <v>14</v>
       </c>
       <c r="AP31" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AQ31" t="n">
         <v>22</v>
@@ -6062,16 +6129,16 @@
         <v>21</v>
       </c>
       <c r="AS31" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AT31" t="n">
         <v>26</v>
       </c>
       <c r="AU31" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AV31" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AW31" t="n">
         <v>9</v>
@@ -6086,7 +6153,7 @@
         <v>7</v>
       </c>
       <c r="BA31" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BB31" t="n">
         <v>24</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>11-23-2008-09</t>
+          <t>2008-11-23</t>
         </is>
       </c>
     </row>
